--- a/pacjenci/MEDYNSKI MARCIN.xlsx
+++ b/pacjenci/MEDYNSKI MARCIN.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Do oceny</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -542,17 +542,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
+          <t>4 - utrzymujący się wychwyt patologiczny</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
+          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
         </is>
       </c>
     </row>

--- a/pacjenci/MEDYNSKI MARCIN.xlsx
+++ b/pacjenci/MEDYNSKI MARCIN.xlsx
@@ -413,235 +413,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>30.08.2022</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina, zakażenie HIV. Ocena wstępna zaawansowania choroby.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 78 min od podania 18F-FDG. Glikemia: 78mg%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nieliczne rozsiane guzki w płucach do 6mm.  Brzuch i miednica: Rozlana aktywność metaboliczna w topografii dna żołądka, SUV max 4,5 - czynnościowa? - do oceny klinicznej i ew. gastroskopowej. Pojedyncze drobne obszary miernie zwiększonej aktywności metabolicznej w powiększonej do 130mm w wymiarze dwubiegunowym śledzionie średnicy wg PET do 12mm, SUV max do 3,0.  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Dość liczne drobne węzły okołoaortalne obustronnie średnicy do 10mm.    Układ kostny: Aktywny metabolicznie obszar w lewobocznej części trzonu mostka średnicy wg PET 10mm, SUV max 4,2. Poza tym wybitnie niejednorodny metabolizm FDG w układzie kostnym.  Wartości referencyjne: MBPS SUVmax 1,7, Prawy płat wątroby SUVmax do 2,6.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono: - wybitnie niejednorodny metabolizm FDG w układzie kostnym z pojedynczym wyodrębniającym się aktywnym metabolicznie obszarem w lewobocznej części trzonu mostka, - pojedyncze drobne obszary miernie zwiększonej aktywności metabolicznej w powiększonej  śledzionie. Nie uwidoczniono aktywnych metabolicznie węzłów chłonnych.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>4.5</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>27.10.2022</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina- rozp.08.2022.  Wczesna ocena odpowiedzi po 2 cyklach ABVD.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 60 min od podania 18F-FDG. Glikemia: 93 mg%</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Asymetryczne wzmożony metabolizm FDG w prawym fałdzie głosowym SUV max 5,1 vs strona lewa 3,2- do ew kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Polipowate zgrubienie błony  śluzowej w prawej zatoce szczękowej. Drobne zgrubienia błony śluzowej w lewej zatoce szczękowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nieliczne rozsiane guzki w płucach do 6mm.  Brzuch i miednica: Wzmożony metabolizm FDG w dnie żołądka SUV max 3,8- odczynowo? Niejednorodny metabolizm FDG w wątrobie i w śledzionie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Dość liczne drobne węzły okołoaortalne obustronnie średnicy do 7mm.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem.  Inne: Symetrycznie wzmożony metabolizm FDG w mięśniach przywodzicieli obu ud - zmiany w pierwszej kolejności o charakterze czynnościowym.  Wartości referencyjne: MBPS SUVmax 1,9 Prawy płat wątroby SUVmax do 2,9.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktualnie badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej w obszarze objętym badaniem.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>5.1</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>23.03.2023</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina NOS, HIV setting. Ocena remisji choroby po zakończeniu ChTh.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 96 mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Wzmożony metabolizm FDG w fałdach głosowych SUV max do 9,7- czynnościowo? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Niewielkie zgrubienia błony śluzowej w lewej zatoce czołowej. Drobne zgrubienia błony śluzowej w obu zatokach szczękowych.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pojedyncze, drobne guzki w płucach wielkości do 4mm. Drobne zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Rozlanie wzmożony metabolizm FDG w żołądku SUV max 4,8- odczynowo? Wzmożony metabolizm FDG w jelitach, zwłaszcza w okolicy krętniczo-kątniczej SUV max 5,2-czynnościowo? Niejednorodny metabolizm FDG w powiększonej wątrobie i w guzowato powiększonej śledzionie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Dość liczne drobne węzły okołoaortalne obustronnie średnicy do 8mm. Węzły chłonne pachwinowe wielkości do 11x8mm.  Układ kostny: Aktywny metabolicznie obszar w głowie kości ramiennej lewej średnicy 16 mm wg PET SUV max 7,5- nowe ognisko. Poza tym fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Niewielkie zmiany zwyrodnieniowe kręgosłupa. Drobne wyspy kostne w kościach udowych i w miednicy.  Inne: Symetrycznie wzmożony metabolizm FDG w mięśniach przywodzicieli obu ud - zmiany w pierwszej kolejności o charakterze czynnościowym/przeciążeniowym.  Wartości referencyjne: MBPS SUVmax 1,9; Prawy płat wątroby SUVmax do 2,7.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie obszaru w głowie kości ramiennej lewej - w pierwszej kolejności nowe ognisko  choroby chłoniakowej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>01.08.2023</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina NOS, HIV setting. Ocena remisji choroby przed outoPBSCT.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 90 mg%.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Wzmożony metabolizm FDG w fałdach głosowych SUV max do 5,3- czynnościowo? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Niewielkie lewowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowaną na stronę lewą. Drobne zgrubienia błony śluzowej w obu zatokach szczękowych.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pojedyncze, drobne guzki w płucach wielkości do 4mm. Drobne zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywne metabolicznie węzły chłonne pachwinowe prawe, wielkości do 12x8mm, SUV max do 5,9. Rozlanie wzmożony metabolizm FDG w żołądku SUV max 4,7- odczynowo? Wzmożony metabolizm FDG w jelitach, zwłaszcza w okolicy krętniczo-kątniczej SUV max 4,5-czynnościowo? Niejednorodny metabolizm FDG w powiększonej wątrobie i w guzowato powiększonej śledzionie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Dość liczne drobne węzły chłonne okołoaortalne obustronnie wielkości do 9x7mm. Węzły chłonne pachwinowe lewe wielkości do 10x8mm.  Układ kostny: Miernie pobudzony metabolicznie obszar w głowie kości ramiennej lewej średnicy 14 mm wg PET SUV max 2,5. Poza tym fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Niewielkie zmiany zwyrodnieniowe kręgosłupa. Os sacrum arcuatum. Drobne wyspy kostne w kościach udowych i w miednicy oraz w prawej łopatce.  Inne: Asymetrycznie wzmożony metabolizm FDG w mięśniu podłopatkowym po stronie prawej i w mięśniu piersiowym większym po tej stronie, SUV max do 3,7 - zmiany w pierwszej kolejności o charakterze czynnościowo-przeciążeniowym.  Wartości referencyjne: MBPS SUVmax 1,7; Prawy płat wątroby SUVmax do 2,7.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność: - miernie pobudzonego metabolicznie obszaru w głowie kości ramiennej lewej - w porównaniu do badania poprzedniego PET z 23.03.2023 znaczna regresja metaboliczna zmian; - aktywnych metabolicznie węzłów chłonnych pachwinowych prawych - do weryfikacji. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>5.9</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4 - wychwyt umiarkowanie większy od wątroby</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Częściowa odpowiedź metaboliczna na leczenie. Klasyfikacja Lugano: Partial Response (PR) - częściowa odpowiedź na leczenie. Deauville: 4 - wychwyt umiarkowanie większy od wątroby.</t>
-        </is>
       </c>
     </row>
   </sheetData>
